--- a/reports/pdf_change_20260819.xlsx
+++ b/reports/pdf_change_20260819.xlsx
@@ -38,11 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
@@ -67,6 +62,11 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -74,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,18 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 136억(2.9%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -588,309 +588,506 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 7억(2.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 4종목  /  매도 2종목</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>감성코퍼레이션</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>113</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>460828690</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.43%→0.50%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>440→553</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-144</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-1480893120</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>1.00%→0.70%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>452→308</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>아모텍</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>462966840</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>1.05%→1.09%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>349→385</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-962230080</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.69%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>263→201</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>955700900</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.43%→1.64%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>116→133</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>하나마이크론</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-33</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-1349224800</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>1.63%→1.48%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>198→165</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>에스피지</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>1689660000</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.93%→1.24%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>35→50</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-24</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-927435600</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.63%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>98→74</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>티에프이</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>481866000</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>0.89%→1.04%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>106→118</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>한중엔시에스</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>-428047200</v>
+      </c>
+      <c r="J10" s="16" t="inlineStr">
+        <is>
+          <t>0.64%→0.49%</t>
+        </is>
+      </c>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>74→62</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>두산테스나</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>902925100</v>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>0.77%→0.94%</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>41→52</t>
+        </is>
+      </c>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
+      <c r="J11" s="17" t="n"/>
+      <c r="K11" s="17" t="n"/>
+    </row>
+    <row r="13" ht="19" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 6억(0.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+    </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>한선엔지니어링</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="n">
-        <v>42</v>
-      </c>
-      <c r="C14" s="13" t="n">
-        <v>39102000</v>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>1.53%→1.67%</t>
-        </is>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>474→516</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>-34</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>-95478800</v>
-      </c>
-      <c r="J14" s="18" t="inlineStr">
-        <is>
-          <t>7.75%→7.42%</t>
-        </is>
-      </c>
-      <c r="K14" s="15" t="inlineStr">
-        <is>
-          <t>795→761</t>
-        </is>
-      </c>
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
+      <c r="J14" s="8" t="n"/>
+      <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>424</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>4027457280</v>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.05%</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>0→424</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>씨어스</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>29123200</v>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>6.17%→6.27%</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
-        <is>
-          <t>977→993</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>인텍플러스</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>-14</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>-32877600</v>
-      </c>
-      <c r="J15" s="18" t="inlineStr">
-        <is>
-          <t>2.62%→2.50%</t>
-        </is>
-      </c>
-      <c r="K15" s="15" t="inlineStr">
-        <is>
-          <t>321→307</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>스피어</t>
-        </is>
-      </c>
-      <c r="B16" s="13" t="n">
-        <v>12</v>
-      </c>
-      <c r="C16" s="13" t="n">
-        <v>24122400</v>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>2.48%→2.56%</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>355→367</t>
-        </is>
-      </c>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="19" t="n"/>
-      <c r="J16" s="19" t="n"/>
-      <c r="K16" s="19" t="n"/>
+      <c r="H16" s="15" t="n">
+        <v>-123</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <v>-1457992800</v>
+      </c>
+      <c r="J16" s="16" t="inlineStr">
+        <is>
+          <t>1.09%→0.69%</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>345→222</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>비나텍</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>27702000</v>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>2.96%→3.06%</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
-        <is>
-          <t>154→159</t>
-        </is>
-      </c>
-      <c r="G17" s="19" t="n"/>
-      <c r="H17" s="19" t="n"/>
-      <c r="I17" s="19" t="n"/>
-      <c r="J17" s="19" t="n"/>
-      <c r="K17" s="19" t="n"/>
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>녹십자</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>-321552000</v>
+      </c>
+      <c r="J17" s="16" t="inlineStr">
+        <is>
+          <t>3.12%→2.99%</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>183→178</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 10억(1.7%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-      <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,774억   ·   현금 41억(1.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
@@ -899,7 +1096,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,346억   ·   현금 25억(1.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -913,20 +1110,417 @@
       <c r="J22" s="4" t="n"/>
       <c r="K22" s="4" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 7억(2.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 4종목  /  매도 2종목</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="8" t="n"/>
+      <c r="J26" s="8" t="n"/>
+      <c r="K26" s="8" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>한선엔지니어링</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>39102000</v>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>1.53%→1.67%</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>474→516</t>
+        </is>
+      </c>
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>-34</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <v>-95478800</v>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>7.75%→7.42%</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>795→761</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>씨어스</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>29123200</v>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>6.17%→6.27%</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>977→993</t>
+        </is>
+      </c>
+      <c r="G29" s="14" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n">
+        <v>-14</v>
+      </c>
+      <c r="I29" s="15" t="n">
+        <v>-32877600</v>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>2.62%→2.50%</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>321→307</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>스피어</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>24122400</v>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>2.48%→2.56%</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>355→367</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>27702000</v>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2.96%→3.06%</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>154→159</t>
+        </is>
+      </c>
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 4억(0.8%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="8" t="n"/>
+      <c r="J34" s="8" t="n"/>
+      <c r="K34" s="8" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>인제니아테라퓨틱스(Reg.S)  (신규)</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="n">
+        <v>655</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>1425797450</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→2.52%</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>0→655</t>
+        </is>
+      </c>
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>한스바이오메드</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>-210</v>
+      </c>
+      <c r="I36" s="15" t="n">
+        <v>-522175500</v>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>2.66%→1.77%</t>
+        </is>
+      </c>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>612→402</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n"/>
+      <c r="C38" s="20" t="n"/>
+      <c r="D38" s="20" t="n"/>
+      <c r="E38" s="20" t="n"/>
+      <c r="F38" s="20" t="n"/>
+      <c r="G38" s="20" t="n"/>
+      <c r="H38" s="20" t="n"/>
+      <c r="I38" s="20" t="n"/>
+      <c r="J38" s="20" t="n"/>
+      <c r="K38" s="20" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A25:K25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A23:K23"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="G26:K26"/>
     <mergeCell ref="A22:K22"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
+    <mergeCell ref="A4:E4"/>
     <mergeCell ref="A20:K20"/>
-    <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A38:K38"/>
     <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A13:K13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260819.xlsx
+++ b/reports/pdf_change_20260819.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,778억   ·   현금 136억(2.9%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 6종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 136억(2.9%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>113</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>460828690</v>
+        <v>459945030</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-144</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1480893120</v>
+        <v>-1478053440</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>36</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>462966840</v>
+        <v>462079080</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-62</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-962230080</v>
+        <v>-960384960</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>17</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>955700900</v>
+        <v>953868300</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-33</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1349224800</v>
+        <v>-1346637600</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1689660000</v>
+        <v>1686420000</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-24</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-927435600</v>
+        <v>-925657200</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>12</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>481866000</v>
+        <v>480942000</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-12</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-428047200</v>
+        <v>-427226400</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>902925100</v>
+        <v>901193700</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,023억   ·   현금 6억(0.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1007,7 +1007,7 @@
         <v>424</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>4027457280</v>
+        <v>4042712800</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>-123</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-1457992800</v>
+        <v>-1463515500</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-321552000</v>
+        <v>-322770000</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,774억   ·   현금 41억(1.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,346억   ·   현금 25억(1.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1120,7 +1120,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 295억   ·   현금 7억(2.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 4종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 7억(2.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1216,11 +1216,11 @@
         <v>42</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>39102000</v>
+        <v>36644160</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>1.53%→1.67%</t>
+          <t>1.47%→1.60%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -1237,11 +1237,11 @@
         <v>-34</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-95478800</v>
+        <v>-95737200</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>7.75%→7.42%</t>
+          <t>7.96%→7.62%</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -1260,11 +1260,11 @@
         <v>16</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>29123200</v>
+        <v>27299200</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>6.17%→6.27%</t>
+          <t>5.93%→6.03%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1281,11 +1281,11 @@
         <v>-14</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-32877600</v>
+        <v>-38570000</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>2.62%→2.50%</t>
+          <t>3.14%→3.01%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1304,11 +1304,11 @@
         <v>12</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>24122400</v>
+        <v>23484000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>2.48%→2.56%</t>
+          <t>2.47%→2.56%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1332,11 +1332,11 @@
         <v>5</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>27702000</v>
+        <v>25308000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>2.96%→3.06%</t>
+          <t>2.77%→2.86%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 586억   ·   현금 4억(0.8%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 4억(0.8%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1449,7 +1449,7 @@
         <v>655</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>1425797450</v>
+        <v>1402230550</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>-210</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-522175500</v>
+        <v>-513544500</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_change_20260819.xlsx
+++ b/reports/pdf_change_20260819.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억   ·   현금 136억(2.9%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 6종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,674억      당일 2026-08-19  vs  전영업일 2026-08-18      매수 6종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -911,7 +911,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억   ·   현금 6억(0.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,837억      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1072,7 +1072,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억   ·   현금 40억(1.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,691억      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1096,7 +1096,7 @@
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억   ·   현금 25억(1.1%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,234억      당일 2026-08-19  vs  전영업일 2026-08-18      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B22" s="4" t="n"/>
@@ -1120,7 +1120,7 @@
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억   ·   현금 7억(2.5%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 4종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 288억      당일 2026-08-19  vs  전영업일 2026-08-18      매수 4종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B25" s="4" t="n"/>
@@ -1353,7 +1353,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억   ·   현금 4억(0.8%)      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 555억      당일 2026-08-19  vs  전영업일 2026-08-18      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
